--- a/plantillas/excel/fase 1/plantilla 1.xlsx
+++ b/plantillas/excel/fase 1/plantilla 1.xlsx
@@ -1,171 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tareas\Año_2026\3.Marzo\plan_next\plantillas\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8637BBA-A08C-4270-A2F7-7FAD4D87CD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{DD192C3D-2FD1-44F5-8007-698C8A60D29B}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="INICIO" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INICIO" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Nombre del Proyecto</t>
-  </si>
-  <si>
-    <t>Rubro / Sector</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Departamento</t>
-  </si>
-  <si>
-    <t>País</t>
-  </si>
-  <si>
-    <t>Moneda</t>
-  </si>
-  <si>
-    <t>Tipo de Cambio (Bs/$us)</t>
-  </si>
-  <si>
-    <t>Tasa de Inflación Anual</t>
-  </si>
-  <si>
-    <t>Horizonte de Proyección (años)</t>
-  </si>
-  <si>
-    <t>Año Base (Año 0)</t>
-  </si>
-  <si>
-    <t>Año Inicio Operaciones</t>
-  </si>
-  <si>
-    <t>Impuesto IUE (%)</t>
-  </si>
-  <si>
-    <t>Impuesto IT (%)</t>
-  </si>
-  <si>
-    <t>PLAN DE NEGOCIO</t>
-  </si>
-  <si>
-    <t>PARÁMETROS GLOBALES</t>
-  </si>
-  <si>
-    <t>N°</t>
-  </si>
-  <si>
-    <t>Nombre del Producto</t>
-  </si>
-  <si>
-    <t>Unidad de Medida</t>
-  </si>
-  <si>
-    <t>Peso/Vol por Unidad</t>
-  </si>
-  <si>
-    <t>PRODUCTOS / SERVICIOS</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="11">
+    <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1A44EB"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color rgb="FF1A44EB"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF1A44EB"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1A44EB"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -182,8 +107,33 @@
         <bgColor rgb="FF2C3E50"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -206,35 +156,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -534,204 +558,355 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8946F2-8DE4-497B-8435-477CADAFFEE4}">
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col width="29.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="28.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="19.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>PLAN DE NEGOCIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PARÁMETROS GLOBALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Nombre del Proyecto</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Rubro / Sector</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Ciudad</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio (Bs/$us)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Tasa de Inflación Anual</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Horizonte de Proyección (años)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Año Base (Año 0)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Año Inicio Operaciones</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Impuesto IUE (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Impuesto IT (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCTOS / SERVICIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Nombre del Producto</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Unidad de Medida</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Peso/Vol por Unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="7"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="9"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>1</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>2</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>3</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>4</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>6</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>7</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>8</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>9</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>10</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>DATOS DEL NEGOCIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Horario de Atención</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Zona / Dirección</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Canal de Venta</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Capacidad Diaria (unidades)</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>BUYER PERSONA / SEGMENTACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Edad Objetivo (rango)</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Género Objetivo</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Ocupación Principal</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Zona de Residencia Objetivo</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Motivaciones de Compra</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Canal de Información Preferido</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Nivel Socioeconómico (NSE)</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A31:B31"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>